--- a/artfynd/A 2282-2026 artfynd.xlsx
+++ b/artfynd/A 2282-2026 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>131292176</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>131292178</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>131292266</v>
       </c>
       <c r="B5" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>131292262</v>
       </c>
       <c r="B6" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>131292180</v>
       </c>
       <c r="B7" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>131292179</v>
       </c>
       <c r="B8" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>131292269</v>
       </c>
       <c r="B10" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131292177</v>
+        <v>131292253</v>
       </c>
       <c r="B11" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,26 +1817,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1844,10 +1849,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529236</v>
+        <v>529240</v>
       </c>
       <c r="R11" t="n">
-        <v>7000619</v>
+        <v>7000575</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1884,7 +1889,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran med ringhack.</t>
+          <t>Ringhack, äldre, på en tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1893,7 +1898,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1904,17 +1908,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1932,10 +1936,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131292253</v>
+        <v>131292177</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,31 +1947,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1975,10 +1974,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529240</v>
+        <v>529236</v>
       </c>
       <c r="R12" t="n">
-        <v>7000575</v>
+        <v>7000619</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2015,7 +2014,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en tall.</t>
+          <t>Långväxta bålar på en gran med ringhack.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2024,6 +2023,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2034,17 +2034,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2065,7 +2065,7 @@
         <v>131292268</v>
       </c>
       <c r="B13" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 2282-2026 artfynd.xlsx
+++ b/artfynd/A 2282-2026 artfynd.xlsx
@@ -1806,10 +1806,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131292253</v>
+        <v>131292177</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,31 +1817,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1849,10 +1844,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529240</v>
+        <v>529236</v>
       </c>
       <c r="R11" t="n">
-        <v>7000575</v>
+        <v>7000619</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1889,7 +1884,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en tall.</t>
+          <t>Långväxta bålar på en gran med ringhack.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1898,6 +1893,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1908,17 +1904,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1936,10 +1932,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131292177</v>
+        <v>131292253</v>
       </c>
       <c r="B12" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1947,26 +1943,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1974,10 +1975,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529236</v>
+        <v>529240</v>
       </c>
       <c r="R12" t="n">
-        <v>7000619</v>
+        <v>7000575</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2014,7 +2015,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran med ringhack.</t>
+          <t>Ringhack, äldre, på en tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2023,7 +2024,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2034,17 +2034,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 2282-2026 artfynd.xlsx
+++ b/artfynd/A 2282-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131292150</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131292176</v>
+        <v>131292178</v>
       </c>
       <c r="B3" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529228</v>
+        <v>529170</v>
       </c>
       <c r="R3" t="n">
-        <v>7000597</v>
+        <v>7000645</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,11 +884,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -936,10 +931,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131292178</v>
+        <v>131292176</v>
       </c>
       <c r="B4" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529170</v>
+        <v>529228</v>
       </c>
       <c r="R4" t="n">
-        <v>7000645</v>
+        <v>7000597</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,6 +1005,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1060,7 +1060,7 @@
         <v>131292266</v>
       </c>
       <c r="B5" t="n">
-        <v>91810</v>
+        <v>91812</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>131292262</v>
       </c>
       <c r="B6" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>131292180</v>
       </c>
       <c r="B7" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>131292179</v>
       </c>
       <c r="B8" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>131292252</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>131292269</v>
       </c>
       <c r="B10" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>131292177</v>
       </c>
       <c r="B11" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>131292253</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>131292268</v>
       </c>
       <c r="B13" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 2282-2026 artfynd.xlsx
+++ b/artfynd/A 2282-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131292150</v>
       </c>
       <c r="B2" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131292178</v>
+        <v>131292176</v>
       </c>
       <c r="B3" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529170</v>
+        <v>529228</v>
       </c>
       <c r="R3" t="n">
-        <v>7000645</v>
+        <v>7000597</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,6 +884,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,10 +936,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131292176</v>
+        <v>131292178</v>
       </c>
       <c r="B4" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529228</v>
+        <v>529170</v>
       </c>
       <c r="R4" t="n">
-        <v>7000597</v>
+        <v>7000645</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,11 +1010,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1060,7 +1060,7 @@
         <v>131292266</v>
       </c>
       <c r="B5" t="n">
-        <v>91812</v>
+        <v>91813</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>131292262</v>
       </c>
       <c r="B6" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>131292180</v>
       </c>
       <c r="B7" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>131292179</v>
       </c>
       <c r="B8" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>131292252</v>
       </c>
       <c r="B9" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>131292269</v>
       </c>
       <c r="B10" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>131292177</v>
       </c>
       <c r="B11" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>131292253</v>
       </c>
       <c r="B12" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>131292268</v>
       </c>
       <c r="B13" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 2282-2026 artfynd.xlsx
+++ b/artfynd/A 2282-2026 artfynd.xlsx
@@ -810,7 +810,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131292176</v>
+        <v>131292178</v>
       </c>
       <c r="B3" t="n">
         <v>79249</v>
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529228</v>
+        <v>529170</v>
       </c>
       <c r="R3" t="n">
-        <v>7000597</v>
+        <v>7000645</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,11 +884,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -936,7 +931,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131292178</v>
+        <v>131292176</v>
       </c>
       <c r="B4" t="n">
         <v>79249</v>
@@ -974,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529170</v>
+        <v>529228</v>
       </c>
       <c r="R4" t="n">
-        <v>7000645</v>
+        <v>7000597</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,6 +1005,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 2282-2026 artfynd.xlsx
+++ b/artfynd/A 2282-2026 artfynd.xlsx
@@ -810,7 +810,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131292178</v>
+        <v>131292176</v>
       </c>
       <c r="B3" t="n">
         <v>79249</v>
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529170</v>
+        <v>529228</v>
       </c>
       <c r="R3" t="n">
-        <v>7000645</v>
+        <v>7000597</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,6 +884,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,7 +936,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131292176</v>
+        <v>131292178</v>
       </c>
       <c r="B4" t="n">
         <v>79249</v>
@@ -969,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529228</v>
+        <v>529170</v>
       </c>
       <c r="R4" t="n">
-        <v>7000597</v>
+        <v>7000645</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,11 +1010,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1806,10 +1806,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131292177</v>
+        <v>131292253</v>
       </c>
       <c r="B11" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,26 +1817,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1844,10 +1849,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529236</v>
+        <v>529240</v>
       </c>
       <c r="R11" t="n">
-        <v>7000619</v>
+        <v>7000575</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1884,7 +1889,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran med ringhack.</t>
+          <t>Ringhack, äldre, på en tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1893,7 +1898,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1904,17 +1908,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1932,10 +1936,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131292253</v>
+        <v>131292177</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,31 +1947,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1975,10 +1974,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529240</v>
+        <v>529236</v>
       </c>
       <c r="R12" t="n">
-        <v>7000575</v>
+        <v>7000619</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2015,7 +2014,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en tall.</t>
+          <t>Långväxta bålar på en gran med ringhack.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2024,6 +2023,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2034,17 +2034,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 2282-2026 artfynd.xlsx
+++ b/artfynd/A 2282-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131292150</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131292176</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>131292178</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>131292266</v>
       </c>
       <c r="B5" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>131292262</v>
       </c>
       <c r="B6" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>131292180</v>
       </c>
       <c r="B7" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>131292179</v>
       </c>
       <c r="B8" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>131292252</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>131292269</v>
       </c>
       <c r="B10" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131292253</v>
+        <v>131292177</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,31 +1817,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1849,10 +1844,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529240</v>
+        <v>529236</v>
       </c>
       <c r="R11" t="n">
-        <v>7000575</v>
+        <v>7000619</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1889,7 +1884,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en tall.</t>
+          <t>Långväxta bålar på en gran med ringhack.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1898,6 +1893,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1908,17 +1904,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1936,10 +1932,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131292177</v>
+        <v>131292253</v>
       </c>
       <c r="B12" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1947,26 +1943,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1974,10 +1975,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529236</v>
+        <v>529240</v>
       </c>
       <c r="R12" t="n">
-        <v>7000619</v>
+        <v>7000575</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2014,7 +2015,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran med ringhack.</t>
+          <t>Ringhack, äldre, på en tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2023,7 +2024,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2034,17 +2034,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2065,7 +2065,7 @@
         <v>131292268</v>
       </c>
       <c r="B13" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 2282-2026 artfynd.xlsx
+++ b/artfynd/A 2282-2026 artfynd.xlsx
@@ -1806,10 +1806,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131292177</v>
+        <v>131292253</v>
       </c>
       <c r="B11" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,26 +1817,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1844,10 +1849,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529236</v>
+        <v>529240</v>
       </c>
       <c r="R11" t="n">
-        <v>7000619</v>
+        <v>7000575</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1884,7 +1889,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran med ringhack.</t>
+          <t>Ringhack, äldre, på en tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1893,7 +1898,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1904,17 +1908,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1932,10 +1936,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131292253</v>
+        <v>131292177</v>
       </c>
       <c r="B12" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,31 +1947,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1975,10 +1974,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529240</v>
+        <v>529236</v>
       </c>
       <c r="R12" t="n">
-        <v>7000575</v>
+        <v>7000619</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2015,7 +2014,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en tall.</t>
+          <t>Långväxta bålar på en gran med ringhack.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2024,6 +2023,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2034,17 +2034,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 2282-2026 artfynd.xlsx
+++ b/artfynd/A 2282-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131292150</v>
       </c>
       <c r="B2" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131292176</v>
       </c>
       <c r="B3" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>131292178</v>
       </c>
       <c r="B4" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>131292266</v>
       </c>
       <c r="B5" t="n">
-        <v>91814</v>
+        <v>91817</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>131292262</v>
       </c>
       <c r="B6" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>131292180</v>
       </c>
       <c r="B7" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>131292179</v>
       </c>
       <c r="B8" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>131292252</v>
       </c>
       <c r="B9" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>131292269</v>
       </c>
       <c r="B10" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131292253</v>
+        <v>131292177</v>
       </c>
       <c r="B11" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,31 +1817,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1849,10 +1844,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529240</v>
+        <v>529236</v>
       </c>
       <c r="R11" t="n">
-        <v>7000575</v>
+        <v>7000619</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1889,7 +1884,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en tall.</t>
+          <t>Långväxta bålar på en gran med ringhack.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1898,6 +1893,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1908,17 +1904,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1936,10 +1932,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131292177</v>
+        <v>131292253</v>
       </c>
       <c r="B12" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1947,26 +1943,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1974,10 +1975,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529236</v>
+        <v>529240</v>
       </c>
       <c r="R12" t="n">
-        <v>7000619</v>
+        <v>7000575</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2014,7 +2015,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran med ringhack.</t>
+          <t>Ringhack, äldre, på en tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2023,7 +2024,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2034,17 +2034,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2065,7 +2065,7 @@
         <v>131292268</v>
       </c>
       <c r="B13" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 2282-2026 artfynd.xlsx
+++ b/artfynd/A 2282-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131292150</v>
       </c>
       <c r="B2" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131292176</v>
       </c>
       <c r="B3" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>131292178</v>
       </c>
       <c r="B4" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>131292266</v>
       </c>
       <c r="B5" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>131292262</v>
       </c>
       <c r="B6" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>131292180</v>
       </c>
       <c r="B7" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>131292179</v>
       </c>
       <c r="B8" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>131292252</v>
       </c>
       <c r="B9" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>131292269</v>
       </c>
       <c r="B10" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131292177</v>
+        <v>131292253</v>
       </c>
       <c r="B11" t="n">
-        <v>79253</v>
+        <v>57892</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,26 +1817,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1844,10 +1849,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529236</v>
+        <v>529240</v>
       </c>
       <c r="R11" t="n">
-        <v>7000619</v>
+        <v>7000575</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1884,7 +1889,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran med ringhack.</t>
+          <t>Ringhack, äldre, på en tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1893,7 +1898,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1904,17 +1908,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1932,10 +1936,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131292253</v>
+        <v>131292177</v>
       </c>
       <c r="B12" t="n">
-        <v>57891</v>
+        <v>79254</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,31 +1947,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1975,10 +1974,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529240</v>
+        <v>529236</v>
       </c>
       <c r="R12" t="n">
-        <v>7000575</v>
+        <v>7000619</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2015,7 +2014,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en tall.</t>
+          <t>Långväxta bålar på en gran med ringhack.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2024,6 +2023,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2034,17 +2034,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2065,7 +2065,7 @@
         <v>131292268</v>
       </c>
       <c r="B13" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 2282-2026 artfynd.xlsx
+++ b/artfynd/A 2282-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131292150</v>
       </c>
       <c r="B2" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131292176</v>
       </c>
       <c r="B3" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>131292178</v>
       </c>
       <c r="B4" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>131292266</v>
       </c>
       <c r="B5" t="n">
-        <v>91818</v>
+        <v>91824</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>131292262</v>
       </c>
       <c r="B6" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>131292180</v>
       </c>
       <c r="B7" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>131292179</v>
       </c>
       <c r="B8" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>131292252</v>
       </c>
       <c r="B9" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>131292269</v>
       </c>
       <c r="B10" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131292253</v>
+        <v>131292177</v>
       </c>
       <c r="B11" t="n">
-        <v>57892</v>
+        <v>79260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,31 +1817,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1849,10 +1844,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529240</v>
+        <v>529236</v>
       </c>
       <c r="R11" t="n">
-        <v>7000575</v>
+        <v>7000619</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1889,7 +1884,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en tall.</t>
+          <t>Långväxta bålar på en gran med ringhack.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1898,6 +1893,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1908,17 +1904,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1936,10 +1932,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131292177</v>
+        <v>131292253</v>
       </c>
       <c r="B12" t="n">
-        <v>79254</v>
+        <v>57898</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1947,26 +1943,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1974,10 +1975,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529236</v>
+        <v>529240</v>
       </c>
       <c r="R12" t="n">
-        <v>7000619</v>
+        <v>7000575</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2014,7 +2015,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran med ringhack.</t>
+          <t>Ringhack, äldre, på en tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2023,7 +2024,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2034,17 +2034,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2065,7 +2065,7 @@
         <v>131292268</v>
       </c>
       <c r="B13" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 2282-2026 artfynd.xlsx
+++ b/artfynd/A 2282-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131292150</v>
       </c>
       <c r="B2" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131292176</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>131292178</v>
       </c>
       <c r="B4" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>131292266</v>
       </c>
       <c r="B5" t="n">
-        <v>91824</v>
+        <v>91825</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>131292262</v>
       </c>
       <c r="B6" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>131292180</v>
       </c>
       <c r="B7" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>131292179</v>
       </c>
       <c r="B8" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>131292252</v>
       </c>
       <c r="B9" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>131292269</v>
       </c>
       <c r="B10" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>131292177</v>
       </c>
       <c r="B11" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>131292253</v>
       </c>
       <c r="B12" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>131292268</v>
       </c>
       <c r="B13" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 2282-2026 artfynd.xlsx
+++ b/artfynd/A 2282-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131292150</v>
       </c>
       <c r="B2" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131292176</v>
       </c>
       <c r="B3" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>131292178</v>
       </c>
       <c r="B4" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>131292266</v>
       </c>
       <c r="B5" t="n">
-        <v>91825</v>
+        <v>91828</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>131292262</v>
       </c>
       <c r="B6" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>131292180</v>
       </c>
       <c r="B7" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>131292179</v>
       </c>
       <c r="B8" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>131292252</v>
       </c>
       <c r="B9" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>131292269</v>
       </c>
       <c r="B10" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>131292177</v>
       </c>
       <c r="B11" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>131292253</v>
       </c>
       <c r="B12" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>131292268</v>
       </c>
       <c r="B13" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 2282-2026 artfynd.xlsx
+++ b/artfynd/A 2282-2026 artfynd.xlsx
@@ -810,7 +810,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131292176</v>
+        <v>131292178</v>
       </c>
       <c r="B3" t="n">
         <v>79264</v>
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529228</v>
+        <v>529170</v>
       </c>
       <c r="R3" t="n">
-        <v>7000597</v>
+        <v>7000645</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,11 +884,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -936,7 +931,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131292178</v>
+        <v>131292176</v>
       </c>
       <c r="B4" t="n">
         <v>79264</v>
@@ -974,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529170</v>
+        <v>529228</v>
       </c>
       <c r="R4" t="n">
-        <v>7000645</v>
+        <v>7000597</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,6 +1005,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 2282-2026 artfynd.xlsx
+++ b/artfynd/A 2282-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131292150</v>
       </c>
       <c r="B2" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131292178</v>
+        <v>131292176</v>
       </c>
       <c r="B3" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529170</v>
+        <v>529228</v>
       </c>
       <c r="R3" t="n">
-        <v>7000645</v>
+        <v>7000597</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,6 +884,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,10 +936,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131292176</v>
+        <v>131292178</v>
       </c>
       <c r="B4" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529228</v>
+        <v>529170</v>
       </c>
       <c r="R4" t="n">
-        <v>7000597</v>
+        <v>7000645</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,11 +1010,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1060,7 +1060,7 @@
         <v>131292266</v>
       </c>
       <c r="B5" t="n">
-        <v>91828</v>
+        <v>91834</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>131292262</v>
       </c>
       <c r="B6" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>131292180</v>
       </c>
       <c r="B7" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>131292179</v>
       </c>
       <c r="B8" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>131292252</v>
       </c>
       <c r="B9" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>131292269</v>
       </c>
       <c r="B10" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>131292177</v>
       </c>
       <c r="B11" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>131292253</v>
       </c>
       <c r="B12" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>131292268</v>
       </c>
       <c r="B13" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
